--- a/data/trans_camb/P6901-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6901-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,55; -1,44</t>
+          <t>-28,14; -0,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,4; 4,47</t>
+          <t>-23,03; 4,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 11,68</t>
+          <t>-15,88; 12,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 6,02</t>
+          <t>-31,03; 4,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 18,26</t>
+          <t>-19,23; 20,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,17; 17,05</t>
+          <t>-54,37; 14,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,21; -3,53</t>
+          <t>-23,4; -2,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 5,75</t>
+          <t>-18,1; 5,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 7,66</t>
+          <t>-30,31; 8,07</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,9; -1,14</t>
+          <t>-31,71; -0,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 5,13</t>
+          <t>-25,7; 5,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 14,29</t>
+          <t>-18,1; 15,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 7,14</t>
+          <t>-34,51; 5,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 23,62</t>
+          <t>-20,0; 27,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,12; 20,88</t>
+          <t>-60,43; 17,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,7; -4,34</t>
+          <t>-26,98; -2,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 6,85</t>
+          <t>-20,46; 6,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 9,14</t>
+          <t>-34,69; 9,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 7,12</t>
+          <t>-8,36; 7,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 8,43</t>
+          <t>-6,58; 8,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 9,69</t>
+          <t>-5,53; 9,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 11,67</t>
+          <t>-6,12; 12,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 16,83</t>
+          <t>-0,76; 16,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 11,4</t>
+          <t>-6,54; 10,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 6,72</t>
+          <t>-4,5; 7,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 9,62</t>
+          <t>-2,52; 9,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 8,7</t>
+          <t>-2,13; 9,25</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 9,73</t>
+          <t>-10,42; 10,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 11,55</t>
+          <t>-8,24; 12,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 13,3</t>
+          <t>-6,98; 12,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 14,9</t>
+          <t>-7,08; 15,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 21,85</t>
+          <t>-0,77; 21,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 14,91</t>
+          <t>-7,42; 13,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 8,77</t>
+          <t>-5,59; 9,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 12,59</t>
+          <t>-2,94; 12,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 11,52</t>
+          <t>-2,66; 12,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 32,77</t>
+          <t>-3,15; 35,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 23,25</t>
+          <t>-12,68; 22,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 11,11</t>
+          <t>-25,66; 11,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 13,37</t>
+          <t>-22,89; 14,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 24,43</t>
+          <t>-6,18; 25,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 13,6</t>
+          <t>-17,83; 12,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 20,06</t>
+          <t>-7,6; 19,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 20,01</t>
+          <t>-2,49; 21,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 8,73</t>
+          <t>-14,5; 8,42</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 72,01</t>
+          <t>-5,26; 79,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 50,81</t>
+          <t>-19,97; 50,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,25; 26,24</t>
+          <t>-42,19; 24,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 23,99</t>
+          <t>-32,04; 25,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 45,49</t>
+          <t>-8,48; 46,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 26,37</t>
+          <t>-24,04; 23,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 38,99</t>
+          <t>-11,98; 37,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 38,69</t>
+          <t>-3,94; 41,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 16,9</t>
+          <t>-23,11; 16,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 5,63</t>
+          <t>-7,24; 6,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 5,99</t>
+          <t>-7,31; 5,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 4,47</t>
+          <t>-8,6; 4,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 8,13</t>
+          <t>-7,69; 7,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 14,08</t>
+          <t>-0,84; 14,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 7,89</t>
+          <t>-7,45; 7,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 5,23</t>
+          <t>-5,73; 4,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 7,47</t>
+          <t>-2,51; 7,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 4,68</t>
+          <t>-5,44; 5,17</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 7,57</t>
+          <t>-9,36; 8,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 8,22</t>
+          <t>-9,38; 8,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 5,98</t>
+          <t>-11,15; 6,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 10,99</t>
+          <t>-9,46; 9,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 19,53</t>
+          <t>-0,96; 19,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 10,73</t>
+          <t>-9,09; 10,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 7,12</t>
+          <t>-7,33; 5,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 10,21</t>
+          <t>-3,17; 10,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 6,37</t>
+          <t>-7,02; 7,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6901-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6901-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,9</t>
+          <t>7,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,89</t>
+          <t>2,98</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,14; -0,14</t>
+          <t>-27,99; -2,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 4,33</t>
+          <t>-23,78; 3,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 12,44</t>
+          <t>-15,4; 10,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 4,2</t>
+          <t>-31,05; 6,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 20,99</t>
+          <t>-15,32; 20,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,37; 14,7</t>
+          <t>-6,72; 22,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,4; -2,21</t>
+          <t>-25,19; -3,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 5,07</t>
+          <t>-18,26; 5,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 8,07</t>
+          <t>-6,5; 11,96</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-11,71%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-5,7%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,71; -0,15</t>
+          <t>-31,94; -2,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,7; 5,21</t>
+          <t>-26,76; 3,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 15,4</t>
+          <t>-17,51; 12,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 5,63</t>
+          <t>-33,74; 8,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 27,84</t>
+          <t>-16,77; 26,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,43; 17,71</t>
+          <t>-6,86; 31,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,98; -2,94</t>
+          <t>-28,73; -3,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 6,06</t>
+          <t>-20,82; 5,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 9,45</t>
+          <t>-7,33; 14,58</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>4,34</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>2,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 7,34</t>
+          <t>-8,29; 7,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 8,82</t>
+          <t>-6,89; 8,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 9,29</t>
+          <t>-2,85; 11,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 12,22</t>
+          <t>-7,07; 11,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 16,38</t>
+          <t>-0,01; 16,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 10,67</t>
+          <t>-9,49; 7,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 7,2</t>
+          <t>-5,0; 7,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 9,44</t>
+          <t>-1,49; 9,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 9,25</t>
+          <t>-2,14; 8,18</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>-1,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 10,16</t>
+          <t>-10,4; 9,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 12,13</t>
+          <t>-8,49; 12,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 12,81</t>
+          <t>-3,57; 15,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 15,88</t>
+          <t>-8,08; 15,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 21,46</t>
+          <t>-0,01; 20,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 13,92</t>
+          <t>-10,67; 9,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 9,5</t>
+          <t>-6,24; 9,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 12,64</t>
+          <t>-1,83; 13,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 12,46</t>
+          <t>-2,64; 10,91</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,3</t>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,07</t>
+          <t>-1,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 35,09</t>
+          <t>-4,2; 31,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 22,89</t>
+          <t>-12,5; 23,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 11,17</t>
+          <t>-24,74; 11,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 14,57</t>
+          <t>-22,7; 13,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 25,55</t>
+          <t>-6,47; 25,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 12,56</t>
+          <t>-15,88; 13,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 19,14</t>
+          <t>-7,06; 19,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 21,53</t>
+          <t>-3,46; 21,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 8,42</t>
+          <t>-12,56; 10,24</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-11,86%</t>
+          <t>-8,94%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-4,18%</t>
+          <t>-1,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-5,25%</t>
+          <t>-2,35%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 79,66</t>
+          <t>-7,21; 70,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 50,79</t>
+          <t>-21,58; 54,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 24,39</t>
+          <t>-40,89; 27,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 25,79</t>
+          <t>-31,78; 24,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 46,38</t>
+          <t>-8,78; 46,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,04; 23,07</t>
+          <t>-21,46; 25,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 37,08</t>
+          <t>-10,78; 36,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 41,28</t>
+          <t>-5,63; 41,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 16,01</t>
+          <t>-19,43; 20,03</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,42</t>
+          <t>-0,3</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>0,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 6,08</t>
+          <t>-7,2; 5,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 5,66</t>
+          <t>-7,61; 5,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 4,48</t>
+          <t>-6,98; 5,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 7,15</t>
+          <t>-8,41; 8,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 14,08</t>
+          <t>-1,15; 14,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 7,92</t>
+          <t>-7,46; 6,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 4,27</t>
+          <t>-5,3; 4,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 7,19</t>
+          <t>-2,65; 7,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 5,17</t>
+          <t>-4,52; 4,24</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-3,23%</t>
+          <t>-0,41%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>-0,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-0,8%</t>
+          <t>0,11%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 8,49</t>
+          <t>-9,27; 7,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 8,01</t>
+          <t>-9,78; 7,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 6,07</t>
+          <t>-9,0; 7,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 9,64</t>
+          <t>-10,44; 10,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 19,26</t>
+          <t>-1,39; 20,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 10,7</t>
+          <t>-9,18; 9,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 5,83</t>
+          <t>-6,7; 6,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 10,01</t>
+          <t>-3,33; 10,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 7,01</t>
+          <t>-5,8; 5,72</t>
         </is>
       </c>
     </row>
